--- a/data/BD_EURIBOR.xlsx
+++ b/data/BD_EURIBOR.xlsx
@@ -1,41 +1,107 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="360" yWindow="510" windowWidth="28215" windowHeight="11955" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diccionario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" r:id="rId1"/>
+    <sheet name="Diccionario" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="125725"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>EURIBOR</t>
+  </si>
+  <si>
+    <t>HICP</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Unidad</t>
+  </si>
+  <si>
+    <t>Fecha de la observacion (trimestral)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Tipo de interes EURIBOR</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Indice Armonizado de Precios al Consumo (Harmonized Index of Consumer Prices)</t>
+  </si>
+  <si>
+    <t>indice (base 100)</t>
+  </si>
+  <si>
+    <t>Balanza de pagos, cuenta corriente neta (Balance of Payments, net current account)</t>
+  </si>
+  <si>
+    <t>millones EUR</t>
+  </si>
+  <si>
+    <t>Deficit publico, cuentas no financieras netas (Government Deficit, net non-financial accounts)</t>
+  </si>
+  <si>
+    <t>Nota</t>
+  </si>
+  <si>
+    <t>Fuente: Eurostat (2018) y EMMI (2018). Serie trimestral desestacionalizada, 47 observaciones, enero 2002 - julio 2013.</t>
+  </si>
+  <si>
+    <t>Usada en Computational Statistics (2020) 35:647-666, https://doi.org/10.1007/s00180-019-00922-x</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,10 +116,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -61,84 +135,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -426,844 +433,829 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>EURIBOR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>HICP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
         <v>37257</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>3.626032258064515</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>92.92</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>17211</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>-51384</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
         <v>37347</v>
       </c>
-      <c r="B3" t="n">
-        <v>3.898730158730159</v>
-      </c>
-      <c r="C3" t="n">
-        <v>93.84999999999999</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="B3">
+        <v>3.8987301587301588</v>
+      </c>
+      <c r="C3">
+        <v>93.85</v>
+      </c>
+      <c r="D3">
         <v>2724</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>-49567.1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
         <v>37438</v>
       </c>
-      <c r="B4" t="n">
-        <v>3.446742424242424</v>
-      </c>
-      <c r="C4" t="n">
-        <v>93.93000000000001</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B4">
+        <v>3.4467424242424238</v>
+      </c>
+      <c r="C4">
+        <v>93.93</v>
+      </c>
+      <c r="D4">
         <v>17232</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>-52128.4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
         <v>37530</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>3.010812500000001</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>94.41</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>9577</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>-53593.3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
         <v>37622</v>
       </c>
-      <c r="B6" t="n">
-        <v>2.542952380952381</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6">
+        <v>2.5429523809523809</v>
+      </c>
+      <c r="C6">
         <v>95.08</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>4117</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>-65480</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
         <v>37712</v>
       </c>
-      <c r="B7" t="n">
-        <v>2.234193548387097</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7">
+        <v>2.2341935483870969</v>
+      </c>
+      <c r="C7">
         <v>95.73</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>-2134</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>-50343.8</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
         <v>37803</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>2.201000000000001</v>
       </c>
-      <c r="C8" t="n">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8">
+        <v>95.9</v>
+      </c>
+      <c r="D8">
         <v>6117</v>
       </c>
-      <c r="E8" t="n">
-        <v>-75646.39999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="E8">
+        <v>-75646.399999999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
         <v>37895</v>
       </c>
-      <c r="B9" t="n">
-        <v>2.363629032258065</v>
-      </c>
-      <c r="C9" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9">
+        <v>2.3636290322580651</v>
+      </c>
+      <c r="C9">
+        <v>96.4</v>
+      </c>
+      <c r="D9">
         <v>10949</v>
       </c>
-      <c r="E9" t="n">
-        <v>-59120.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="E9">
+        <v>-59120.800000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
         <v>37987</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>2.14</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>96.77</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>18360</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>-69246.3</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
         <v>38078</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>2.29</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>97.97</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>13646</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>-60313.8</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
         <v>38169</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>2.35</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>98.06</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>8424</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>-56782.9</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13" s="2">
         <v>38261</v>
       </c>
-      <c r="B13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="C13">
         <v>98.67</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>14319</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>-55313.1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:5">
+      <c r="A14" s="2">
         <v>38353</v>
       </c>
-      <c r="B14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="C14" t="n">
-        <v>98.76000000000001</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="B14">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="C14">
+        <v>98.76</v>
+      </c>
+      <c r="D14">
         <v>3885</v>
       </c>
-      <c r="E14" t="n">
-        <v>-67034.39999999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="E14">
+        <v>-67034.399999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2">
         <v>38443</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>2.19</v>
       </c>
-      <c r="C15" t="n">
-        <v>99.95999999999999</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C15">
+        <v>99.96</v>
+      </c>
+      <c r="D15">
         <v>4493</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>-61942.8</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+    <row r="16" spans="1:5">
+      <c r="A16" s="2">
         <v>38534</v>
       </c>
-      <c r="B16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C16" t="n">
+      <c r="B16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C16">
         <v>100.3</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>-320</v>
       </c>
-      <c r="E16" t="n">
-        <v>-46258.4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="E16">
+        <v>-46258.400000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2">
         <v>38626</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>2.63</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>100.97</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>-2736</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>-43761.4</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
+    <row r="18" spans="1:5">
+      <c r="A18" s="2">
         <v>38718</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>2.95</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>101.07</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>-6909</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>-37562.6</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+    <row r="19" spans="1:5">
+      <c r="A19" s="2">
         <v>38808</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>3.31</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>102.44</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>-4848</v>
       </c>
-      <c r="E19" t="n">
-        <v>-35609.6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="E19">
+        <v>-35609.599999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2">
         <v>38899</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>3.62</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>102.52</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>-4255</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>-27064</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+    <row r="21" spans="1:5">
+      <c r="A21" s="2">
         <v>38991</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>3.6</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>102.79</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>1347</v>
       </c>
-      <c r="E21" t="n">
-        <v>-32497.2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="E21">
+        <v>-32497.200000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2">
         <v>39083</v>
       </c>
-      <c r="B22" t="n">
-        <v>4.087656250000001</v>
-      </c>
-      <c r="C22" t="n">
+      <c r="B22">
+        <v>4.0876562500000011</v>
+      </c>
+      <c r="C22">
         <v>102.97</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>8781</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>-18389</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+    <row r="23" spans="1:5">
+      <c r="A23" s="2">
         <v>39173</v>
       </c>
-      <c r="B23" t="n">
-        <v>4.381048387096775</v>
-      </c>
-      <c r="C23" t="n">
+      <c r="B23">
+        <v>4.3810483870967749</v>
+      </c>
+      <c r="C23">
         <v>104.38</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>8723</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>-9923.5</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+    <row r="24" spans="1:5">
+      <c r="A24" s="2">
         <v>39264</v>
       </c>
-      <c r="B24" t="n">
-        <v>4.649538461538464</v>
-      </c>
-      <c r="C24" t="n">
+      <c r="B24">
+        <v>4.6495384615384641</v>
+      </c>
+      <c r="C24">
         <v>104.45</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>3662</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>-9727</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+    <row r="25" spans="1:5">
+      <c r="A25" s="2">
         <v>39356</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>4.67653125</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>105.77</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>-17548</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>-23729.9</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:5">
+      <c r="A26" s="2">
         <v>39448</v>
       </c>
-      <c r="B26" t="n">
-        <v>4.475709677419355</v>
-      </c>
-      <c r="C26" t="n">
+      <c r="B26">
+        <v>4.4757096774193554</v>
+      </c>
+      <c r="C26">
         <v>106.43</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>-37041</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>-28909.3</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+    <row r="27" spans="1:5">
+      <c r="A27" s="2">
         <v>39539</v>
       </c>
-      <c r="B27" t="n">
-        <v>5.054453125</v>
-      </c>
-      <c r="C27" t="n">
+      <c r="B27">
+        <v>5.0544531250000002</v>
+      </c>
+      <c r="C27">
         <v>108.18</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>-27624</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>-46527</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:5">
+      <c r="A28" s="2">
         <v>39630</v>
       </c>
-      <c r="B28" t="n">
-        <v>5.367787878787878</v>
-      </c>
-      <c r="C28" t="n">
+      <c r="B28">
+        <v>5.3677878787878779</v>
+      </c>
+      <c r="C28">
         <v>108.49</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>-37723</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>-49654</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
+    <row r="29" spans="1:5">
+      <c r="A29" s="2">
         <v>39722</v>
       </c>
-      <c r="B29" t="n">
-        <v>4.338531249999997</v>
-      </c>
-      <c r="C29" t="n">
+      <c r="B29">
+        <v>4.3385312499999973</v>
+      </c>
+      <c r="C29">
         <v>108.21</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>-43584</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>-81729.7</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+    <row r="30" spans="1:5">
+      <c r="A30" s="2">
         <v>39814</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>2.218380952380953</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>107.46</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>-16070</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>-121227.5</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+    <row r="31" spans="1:5">
+      <c r="A31" s="2">
         <v>39904</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>1.673209677419355</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>108.37</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>-5029</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>-142580.9</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+    <row r="32" spans="1:5">
+      <c r="A32" s="2">
         <v>39995</v>
       </c>
-      <c r="B32" t="n">
-        <v>1.336939393939394</v>
-      </c>
-      <c r="C32" t="n">
+      <c r="B32">
+        <v>1.3369393939393941</v>
+      </c>
+      <c r="C32">
         <v>108.08</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>7294</v>
       </c>
-      <c r="E32" t="n">
-        <v>-164699.2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="E32">
+        <v>-164699.20000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2">
         <v>40087</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>1.238515625</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>108.67</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>85</v>
       </c>
-      <c r="E33" t="n">
-        <v>-152269.2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="E33">
+        <v>-152269.20000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2">
         <v>40179</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>1.223730158730159</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>108.67</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>-4399</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>-162477.4</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+    <row r="35" spans="1:5">
+      <c r="A35" s="2">
         <v>40269</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>1.252825396825398</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>110.12</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>-2431</v>
       </c>
-      <c r="E35" t="n">
-        <v>-128366.4</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="E35">
+        <v>-128366.39999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2">
         <v>40360</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>1.404954545454546</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>109.95</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>2137</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>-169848</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
         <v>40452</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>1.521573770491804</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>110.87</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>-4345</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>-129290.2</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
         <v>40544</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>1.735671875</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>111.36</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>-12643</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>-104646.7</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+    <row r="39" spans="1:5">
+      <c r="A39" s="2">
         <v>40634</v>
       </c>
-      <c r="B39" t="n">
-        <v>2.12752380952381</v>
-      </c>
-      <c r="C39" t="n">
+      <c r="B39">
+        <v>2.1275238095238098</v>
+      </c>
+      <c r="C39">
         <v>113.15</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>-2272</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>-103143.8</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
         <v>40725</v>
       </c>
-      <c r="B40" t="n">
-        <v>2.114196969696969</v>
-      </c>
-      <c r="C40" t="n">
+      <c r="B40">
+        <v>2.1141969696969691</v>
+      </c>
+      <c r="C40">
         <v>112.91</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>-3592</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>-102621.8</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+    <row r="41" spans="1:5">
+      <c r="A41" s="2">
         <v>40817</v>
       </c>
-      <c r="B41" t="n">
-        <v>2.055661290322581</v>
-      </c>
-      <c r="C41" t="n">
+      <c r="B41">
+        <v>2.0556612903225808</v>
+      </c>
+      <c r="C41">
         <v>114.12</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>8071</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>-104240.4</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+    <row r="42" spans="1:5">
+      <c r="A42" s="2">
         <v>40909</v>
       </c>
-      <c r="B42" t="n">
-        <v>1.671046153846154</v>
-      </c>
-      <c r="C42" t="n">
+      <c r="B42">
+        <v>1.6710461538461541</v>
+      </c>
+      <c r="C42">
         <v>114.35</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>12202</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>-82309.3</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+    <row r="43" spans="1:5">
+      <c r="A43" s="2">
         <v>41000</v>
       </c>
-      <c r="B43" t="n">
-        <v>1.281322580645161</v>
-      </c>
-      <c r="C43" t="n">
+      <c r="B43">
+        <v>1.2813225806451609</v>
+      </c>
+      <c r="C43">
         <v>115.93</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>35619</v>
       </c>
-      <c r="E43" t="n">
-        <v>-91620.89999999999</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="E43">
+        <v>-91620.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="2">
         <v>41091</v>
       </c>
-      <c r="B44" t="n">
-        <v>0.896876923076923</v>
-      </c>
-      <c r="C44" t="n">
+      <c r="B44">
+        <v>0.89687692307692302</v>
+      </c>
+      <c r="C44">
         <v>115.78</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>42161</v>
       </c>
-      <c r="E44" t="n">
-        <v>-85054.39999999999</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="E44">
+        <v>-85054.399999999994</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="2">
         <v>41183</v>
       </c>
-      <c r="B45" t="n">
-        <v>0.5996031746031746</v>
-      </c>
-      <c r="C45" t="n">
+      <c r="B45">
+        <v>0.59960317460317458</v>
+      </c>
+      <c r="C45">
         <v>116.75</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>43880</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>-99998.2</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+    <row r="46" spans="1:5">
+      <c r="A46" s="2">
         <v>41275</v>
       </c>
-      <c r="B46" t="n">
-        <v>0.5715967741935482</v>
-      </c>
-      <c r="C46" t="n">
+      <c r="B46">
+        <v>0.57159677419354815</v>
+      </c>
+      <c r="C46">
         <v>116.47</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>52483</v>
       </c>
-      <c r="E46" t="n">
-        <v>-81287.10000000001</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="E46">
+        <v>-81287.100000000006</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2">
         <v>41365</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>0.5060476190476193</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>117.55</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>56376</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>-77738.8</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
+    <row r="48" spans="1:5">
+      <c r="A48" s="2">
         <v>41456</v>
       </c>
-      <c r="B48" t="n">
-        <v>0.5367727272727273</v>
-      </c>
-      <c r="C48" t="n">
+      <c r="B48">
+        <v>0.53677272727272729</v>
+      </c>
+      <c r="C48">
         <v>117.34</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>48981</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>-73003.3</v>
       </c>
     </row>
@@ -1273,144 +1265,106 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col min="1" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fecha de la observacion (trimestral)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EURIBOR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tipo de interes EURIBOR</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HICP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Indice Armonizado de Precios al Consumo (Harmonized Index of Consumer Prices)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>indice (base 100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Balanza de pagos, cuenta corriente neta (Balance of Payments, net current account)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>millones EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GD</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Deficit publico, cuentas no financieras netas (Government Deficit, net non-financial accounts)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>millones EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Nota</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fuente: Eurostat (2018) y EMMI (2018). Serie trimestral desestacionalizada, 47 observaciones, enero 2002 - julio 2013.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Usada en Computational Statistics (2020) 35:647-666, https://doi.org/10.1007/s00180-019-00922-x</t>
-        </is>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>